--- a/main/ig/StructureDefinition-sas-categorie-orientation.xlsx
+++ b/main/ig/StructureDefinition-sas-categorie-orientation.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T14:02:19+00:00</t>
+    <t>2026-10-08T12:45:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
